--- a/docs/oc-regiones/articulos-de-escritorio-y-papeleria/maule.xlsx
+++ b/docs/oc-regiones/articulos-de-escritorio-y-papeleria/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M409"/>
+  <dimension ref="A1:M410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1474.67</v>
+        <v>1462.18</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1411.83</v>
+        <v>1399.87</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>19220.02</v>
+        <v>19018.74</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2451.48</v>
+        <v>2425.81</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3130.61</v>
+        <v>3113.5</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5447.28</v>
+        <v>5417.51</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1862.39</v>
+        <v>1841.64</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2771.33</v>
+        <v>2756.16</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1361.82</v>
+        <v>1354.36</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>896.63</v>
+        <v>895.49</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>801.53</v>
+        <v>800.51</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>980.96</v>
+        <v>979.71</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2019.67</v>
+        <v>2026.88</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2625.78</v>
+        <v>2643.97</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>1068.62</v>
+        <v>1076.02</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1545.69</v>
+        <v>1552.89</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>785.03</v>
+        <v>790.6900000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2569.87</v>
+        <v>2588.4</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>854.87</v>
+        <v>861.03</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3816.29</v>
+        <v>3843.8</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1676.23</v>
+        <v>1688.31</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1449.09</v>
+        <v>1443.12</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1165.59</v>
+        <v>1160.78</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3078.01</v>
+        <v>3065.32</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>36705.21</v>
+        <v>36648.32</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>759.33</v>
+        <v>758.15</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1506.29</v>
+        <v>1514.07</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1328.21</v>
+        <v>1335.07</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>23905.44</v>
+        <v>24074.15</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1767.92</v>
+        <v>1780.4</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2546.76</v>
+        <v>2564.74</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1682.95</v>
+        <v>1661.2</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2036.67</v>
+        <v>2010.34</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3270.72</v>
+        <v>3228.44</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7178.2</v>
+        <v>7085.42</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4059.72</v>
+        <v>4008.16</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3385.55</v>
+        <v>3351.86</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1051.98</v>
+        <v>1041.51</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>6748.89</v>
+        <v>6734.28</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1249.56</v>
+        <v>1246.85</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1111.98</v>
+        <v>1109.58</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1526.96</v>
+        <v>1523.65</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1199.07</v>
+        <v>1194.04</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>778.66</v>
+        <v>775.39</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5191.04</v>
+        <v>5169.27</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>790.95</v>
+        <v>787.63</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>769.99</v>
+        <v>761.0700000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1248.88</v>
+        <v>1234.43</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2035.24</v>
+        <v>2011.69</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2094.46</v>
+        <v>2070.22</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2480.03</v>
+        <v>2459.03</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>34103.54</v>
+        <v>33814.65</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>787.58</v>
+        <v>786.9400000000001</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27745.32</v>
+        <v>27851.81</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3273.14</v>
+        <v>3285.71</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3862.67</v>
+        <v>3872.91</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2956.94</v>
+        <v>2964.78</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1503.23</v>
+        <v>1501.12</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>876.75</v>
+        <v>877.88</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1002.46</v>
+        <v>1003.75</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2477.16</v>
+        <v>2498.33</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1091.49</v>
+        <v>1100.82</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2775.8</v>
+        <v>2805.57</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>15594.42</v>
+        <v>15786.08</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1248.94</v>
+        <v>1264.99</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3232.48</v>
+        <v>3274.02</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1992.38</v>
+        <v>1945.78</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5768.75</v>
+        <v>5685.62</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5657.59</v>
+        <v>5576.06</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3107.3</v>
+        <v>3062.52</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1789.98</v>
+        <v>1764.19</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5842.74</v>
+        <v>5758.54</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2288.55</v>
+        <v>2255.57</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2108.17</v>
+        <v>2080.93</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2231.86</v>
+        <v>2227.47</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>850.21</v>
+        <v>848.54</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>14704.13</v>
+        <v>14675.17</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1635.41</v>
+        <v>1635.42</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>986.42</v>
+        <v>986.4299999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>38407.01</v>
+        <v>38380.77</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3716.92</v>
+        <v>3697.28</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>4763.95</v>
+        <v>4738.79</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2306.05</v>
+        <v>2293.87</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>968.0599999999999</v>
+        <v>962.9400000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>5931.55</v>
+        <v>5900.22</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2644.33</v>
+        <v>2630.36</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2137.72</v>
+        <v>2126.43</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>17108.26</v>
+        <v>17001.05</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>21417.37</v>
+        <v>21283.16</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4096.91</v>
+        <v>4071.24</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>5892.34</v>
+        <v>5930.96</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>69588.75999999999</v>
+        <v>70525.87</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3876.96</v>
+        <v>3929.16</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>4345.78</v>
+        <v>4404.3</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>3920.76</v>
+        <v>3980.45</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>1026.81</v>
+        <v>1051.78</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>10419.47</v>
+        <v>10672.84</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>4942.89</v>
+        <v>5063.09</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>990.8099999999999</v>
+        <v>1014.9</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>2288.01</v>
+        <v>2345.85</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1422.94</v>
+        <v>1458.91</v>
       </c>
     </row>
     <row r="103">
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2041.93</v>
+        <v>2103.84</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2294-48-CM26</t>
+          <t>2294-49-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2300.13</v>
+        <v>2672.8</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2294-49-CM26</t>
+          <t>2294-48-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>2594.14</v>
+        <v>2369.87</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>6773.57</v>
+        <v>6974.9</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1021.12</v>
+        <v>1051.48</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>4133.84</v>
+        <v>4119.12</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4362.31</v>
+        <v>4346.78</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2214.84</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>883.23</v>
+        <v>880.09</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1437.01</v>
+        <v>1431.89</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>2022.26</v>
+        <v>2007.13</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>852.3099999999999</v>
+        <v>845.9299999999999</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1058.58</v>
+        <v>1050.66</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>1316.42</v>
+        <v>1320.24</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4626.65</v>
+        <v>4640.05</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>811.41</v>
+        <v>813.77</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>899.83</v>
+        <v>904.48</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>17399.92</v>
+        <v>17489.8</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1432.94</v>
+        <v>1440.34</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>50063.82</v>
+        <v>50201.26</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1591.97</v>
+        <v>1596.34</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>870.8099999999999</v>
+        <v>873.2</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3719.28</v>
+        <v>3753.11</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>912.77</v>
+        <v>921.0700000000001</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1911.41</v>
+        <v>1928.8</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2509.43</v>
+        <v>2532.26</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3618.18</v>
+        <v>3643.37</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>982.11</v>
+        <v>988.95</v>
       </c>
     </row>
     <row r="131">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>3775.18</v>
+        <v>3801.46</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1079566-58-CM26</t>
+          <t>2294-118-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9465.68</v>
+        <v>5207.83</v>
       </c>
     </row>
     <row r="133">
@@ -8560,13 +8560,13 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>5915.13</v>
+        <v>5956.31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2294-118-CM26</t>
+          <t>1079566-58-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8586,17 +8586,17 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5171.82</v>
+        <v>9531.59</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>893.05</v>
+        <v>898.9299999999999</v>
       </c>
     </row>
     <row r="136">
@@ -8743,13 +8743,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>6059.2</v>
+        <v>6099.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1216090-30-CM26</t>
+          <t>691-3-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>71.395.600-7</t>
+          <t>61.802.007-K</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>CORP CULTURAL DE LA MUNICIPALIDAD DE CURICO</t>
+          <t>Ministerio de Vivienda y Urbanismo</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8789,12 +8789,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K137" t="inlineStr"/>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1325.92</v>
+        <v>2923.78</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>547640-25-CM26</t>
+          <t>1199-49-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8830,17 +8830,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -8865,13 +8865,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>3555.71</v>
+        <v>2746.49</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1907-11-CM26</t>
+          <t>1907-10-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8926,13 +8926,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>11594.11</v>
+        <v>11698.63</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>3843-33-CM26</t>
+          <t>3206-56-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -8987,13 +8987,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>11831.5</v>
+        <v>2322.48</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1907-10-CM26</t>
+          <t>1907-11-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9048,13 +9048,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>11595.36</v>
+        <v>11697.38</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1199-49-CM26</t>
+          <t>547640-25-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9074,17 +9074,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9109,13 +9109,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2722.25</v>
+        <v>3587.38</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>691-3-CM26</t>
+          <t>3843-33-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9140,12 +9140,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>61.802.007-K</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Ministerio de Vivienda y Urbanismo</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9170,13 +9170,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>2897.97</v>
+        <v>11936.88</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3206-56-CM26</t>
+          <t>1216090-30-CM26</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>71.395.600-7</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>CORP CULTURAL DE LA MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2301.98</v>
+        <v>1337.72</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2998.83</v>
+        <v>2995.73</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>870.76</v>
+        <v>864.52</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>8119.65</v>
+        <v>8061.48</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3342.76</v>
+        <v>3318.81</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>8149.57</v>
+        <v>8091.19</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2277.58</v>
+        <v>2261.27</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3322.44</v>
+        <v>3302.86</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>17794.4</v>
+        <v>17689.54</v>
       </c>
     </row>
     <row r="153">
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>2585.36</v>
+        <v>2570.12</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>848-24-CM26</t>
+          <t>1254658-9-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>65.152.298-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>gerencia</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2711.8</v>
+        <v>1152.88</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1254658-9-CM26</t>
+          <t>848-24-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9872,12 +9872,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>65.152.298-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>gerencia</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1159.93</v>
+        <v>2695.32</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2002-10-CM26</t>
+          <t>848-28-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>60.103.005-5</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERPLAC VII REGION								</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>823.4</v>
+        <v>812.71</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3287-91-CM26</t>
+          <t>848-27-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9989,17 +9989,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,13 +10024,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1161.38</v>
+        <v>918.9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>848-25-CM26</t>
+          <t>2002-10-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>60.103.005-5</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t xml:space="preserve">SERPLAC VII REGION								</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10070,12 +10070,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10085,13 +10085,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1888.15</v>
+        <v>820.22</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>848-27-CM26</t>
+          <t>3287-91-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10111,17 +10111,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>922.46</v>
+        <v>1156.9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>848-28-CM26</t>
+          <t>848-25-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>815.86</v>
+        <v>1880.86</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>890.63</v>
+        <v>891.49</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>990.16</v>
+        <v>991.12</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>8908.450000000001</v>
+        <v>8917.040000000001</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3177.9</v>
+        <v>3180.97</v>
       </c>
     </row>
     <row r="165">
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3220.93</v>
+        <v>3224.04</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2291-268-CM26</t>
+          <t>1426095-31-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10538,17 +10538,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2007.07</v>
+        <v>3159.54</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1426095-31-CM26</t>
+          <t>2291-268-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10599,17 +10599,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>3025.91</v>
+        <v>2095.7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1426095-42-CM26</t>
+          <t>4404-23-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10660,17 +10660,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2830.3</v>
+        <v>25926.26</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>4404-23-CM26</t>
+          <t>848-32-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>25194.45</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>848-32-CM26</t>
+          <t>1426095-42-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10782,17 +10782,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>868.53</v>
+        <v>2912.51</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1569.28</v>
+        <v>1575.47</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2427.1</v>
+        <v>2433.07</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>4481.44</v>
+        <v>4423.75</v>
       </c>
     </row>
     <row r="174">
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2794.97</v>
+        <v>2775.25</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2046-106-CM26</t>
+          <t>3209-45-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11087,17 +11087,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11122,13 +11122,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1294.77</v>
+        <v>3402.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3209-45-CM26</t>
+          <t>2440-176-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11183,13 +11183,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3417.4</v>
+        <v>1364.54</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2440-176-CM26</t>
+          <t>2046-106-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11209,17 +11209,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1370.67</v>
+        <v>1288.98</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>824-6-CM26</t>
+          <t>1978-186-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11275,12 +11275,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>775.33</v>
+        <v>1983.62</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1978-186-CM26</t>
+          <t>1230872-50-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11331,17 +11331,17 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>65.114.043-9</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Corporación Municipal de Desarrollo Productivo y T</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1981.91</v>
+        <v>823.15</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1230872-50-CM26</t>
+          <t>824-6-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11392,17 +11392,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>65.114.043-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y T</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>822.4400000000001</v>
+        <v>776</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2132-70-CM26</t>
+          <t>3756-169-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2891.84</v>
+        <v>3578.78</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2440-194-CM26</t>
+          <t>3756-171-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11514,17 +11514,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11534,12 +11534,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>1201.19</v>
+        <v>8658.92</v>
       </c>
     </row>
     <row r="183">
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>7786.75</v>
+        <v>7765.27</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>3756-169-CM26</t>
+          <t>2132-70-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,13 +11671,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>3588.68</v>
+        <v>2883.87</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3756-171-CM26</t>
+          <t>2440-194-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11697,17 +11697,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11717,12 +11717,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>8682.870000000001</v>
+        <v>1197.88</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>2080.26</v>
+        <v>2056.24</v>
       </c>
     </row>
     <row r="187">
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>6008.24</v>
+        <v>5938.88</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>3843-63-CM26</t>
+          <t>4716-3-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11885,12 +11885,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.531.000-K</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1688.18</v>
+        <v>882.5</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>4716-3-CM26</t>
+          <t>3843-63-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>61.531.000-K</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE CAPACITACION Y EMPLEO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11961,12 +11961,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>895.87</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2291-444-CM26</t>
+          <t>2291-416-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>854.08</v>
+        <v>6735.27</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1596-88-CM26</t>
+          <t>4426-3-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Servicio Nacional del Patrimonio Cultural</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>5329.81</v>
+        <v>1108.09</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2291-416-CM26</t>
+          <t>1596-88-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12129,12 +12129,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SURTI VENTAS S.A.</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.462.500-5</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>6774.18</v>
+        <v>5299.2</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4426-3-CM26</t>
+          <t>2291-444-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>SURTI VENTAS S.A.</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.462.500-5</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1114.49</v>
+        <v>849.1799999999999</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1970.09</v>
+        <v>1957.47</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>3857.22</v>
+        <v>3840.6</v>
       </c>
     </row>
     <row r="196">
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>1600.86</v>
+        <v>1577.7</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1075337-7522-CM26</t>
+          <t>1075337-7521-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1843.28</v>
+        <v>1536.94</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1075337-7521-CM26</t>
+          <t>1075337-7522-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>1573.55</v>
+        <v>1800.39</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>9711.65</v>
+        <v>9485.67</v>
       </c>
     </row>
     <row r="200">
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2439.4</v>
+        <v>2361.62</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>3766-101-CM26</t>
+          <t>3766-100-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2063.68</v>
+        <v>1439.15</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>848-57-CM26</t>
+          <t>3766-101-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.110.600-4</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PELARCO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1640.82</v>
+        <v>2022.98</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>3766-100-CM26</t>
+          <t>848-57-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.110.600-4</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELARCO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1468.1</v>
+        <v>1608.46</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>919.54</v>
+        <v>901.41</v>
       </c>
     </row>
     <row r="205">
@@ -12952,13 +12952,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>974.8099999999999</v>
+        <v>949.14</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1511-374-CM26</t>
+          <t>848-60-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>815.78</v>
+        <v>2419.4</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1079566-114-CM26</t>
+          <t>675-30-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13044,12 +13044,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>SEREMI Bienes Nacionales VII Región</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>778.96</v>
+        <v>1401.06</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1079566-120-CM26</t>
+          <t>1511-374-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K208" t="inlineStr"/>
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2658.28</v>
+        <v>800.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>675-30-CM26</t>
+          <t>1079566-114-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1426.94</v>
+        <v>764.84</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>848-60-CM26</t>
+          <t>1079566-120-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2464.09</v>
+        <v>2610.07</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>779.73</v>
+        <v>758.85</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>5633.3</v>
+        <v>5482.46</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1051.06</v>
+        <v>1022.92</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>976.9</v>
+        <v>950.75</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>782.95</v>
+        <v>761.99</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3581.47</v>
+        <v>3485.57</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>855.37</v>
+        <v>832.47</v>
       </c>
     </row>
     <row r="218">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>1074.69</v>
+        <v>1079.16</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1335444-17-CM26</t>
+          <t>3209-65-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13771,17 +13771,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>807.84</v>
+        <v>785.75</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1069417-305-CM26</t>
+          <t>1335444-17-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>BLUE MIX SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.283.950-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3298.73</v>
+        <v>814.7</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3209-65-CM26</t>
+          <t>1069417-305-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13893,17 +13893,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>BLUE MIX SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.283.950-2</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>779.14</v>
+        <v>3326.73</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1590.93</v>
+        <v>1588.27</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1064.58</v>
+        <v>1077.68</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>8114.49</v>
+        <v>8214.35</v>
       </c>
     </row>
     <row r="225">
@@ -14172,13 +14172,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3150.23</v>
+        <v>3189</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3696-48-CM26</t>
+          <t>902-109-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14198,17 +14198,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14233,13 +14233,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3047.44</v>
+        <v>1185.62</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2595-152-CM26</t>
+          <t>3696-48-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14264,12 +14264,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -14294,13 +14294,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>3366.02</v>
+        <v>3088.01</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1069417-325-CM26</t>
+          <t>2595-152-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K228" t="inlineStr"/>
@@ -14355,13 +14355,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1178.96</v>
+        <v>3410.83</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>902-109-CM26</t>
+          <t>1069417-325-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14381,17 +14381,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14401,12 +14401,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1170.04</v>
+        <v>1194.66</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2436-438-CM26</t>
+          <t>1057461-549-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -14442,17 +14442,17 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14462,12 +14462,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K230" t="inlineStr"/>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>6236.8</v>
+        <v>970.83</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1057461-549-CM26</t>
+          <t>2436-438-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -14503,17 +14503,17 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -14523,12 +14523,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K231" t="inlineStr"/>
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>958.3200000000001</v>
+        <v>6318.18</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>1472.98</v>
+        <v>1492.2</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1079.04</v>
+        <v>1105.6</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>3695.46</v>
+        <v>3786.41</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>933.1900000000001</v>
+        <v>950.84</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3118.33</v>
+        <v>3177.31</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>1669.65</v>
+        <v>1701.23</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2207.09</v>
+        <v>2248.84</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>3408.76</v>
+        <v>3473.23</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>784.29</v>
+        <v>799.13</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>2282.25</v>
+        <v>2308.21</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>880.21</v>
+        <v>890.22</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2011.39</v>
+        <v>2029.51</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1113.47</v>
+        <v>1120.59</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1670.22</v>
+        <v>1675.47</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>11058.63</v>
+        <v>11104.47</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>793.0700000000001</v>
+        <v>796.36</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>779.29</v>
+        <v>782.52</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>788</v>
+        <v>789.64</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>2780.9</v>
+        <v>2786.66</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>3850.12</v>
+        <v>3858.1</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>10125.8</v>
+        <v>10082.31</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1278.88</v>
+        <v>1273.39</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>2838.42</v>
+        <v>2814.21</v>
       </c>
     </row>
     <row r="255">
@@ -16002,13 +16002,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1619.97</v>
+        <v>1628.69</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>4085-284-CM26</t>
+          <t>4085-283-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>76.993.355-7</t>
         </is>
       </c>
       <c r="K256" t="inlineStr"/>
@@ -16063,13 +16063,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2947.54</v>
+        <v>2089.89</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>4085-283-CM26</t>
+          <t>4085-284-CM26</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -16109,12 +16109,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>IMPORTADORA  Y DISTRIBUIDORA BLANMAR SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>76.993.355-7</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K257" t="inlineStr"/>
@@ -16124,13 +16124,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>2078.7</v>
+        <v>2963.41</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2595-180-CM26</t>
+          <t>4085-280-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -16155,12 +16155,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.130.600-3</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -16170,12 +16170,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K258" t="inlineStr"/>
@@ -16185,13 +16185,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>2651.81</v>
+        <v>1718.44</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>4085-280-CM26</t>
+          <t>4085-282-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K259" t="inlineStr"/>
@@ -16246,13 +16246,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1709.24</v>
+        <v>1235.06</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4085-282-CM26</t>
+          <t>2595-180-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -16272,17 +16272,17 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>69.130.600-3</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONGAVI</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -16292,12 +16292,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K260" t="inlineStr"/>
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1228.45</v>
+        <v>2666.09</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>3246.64</v>
+        <v>3282.95</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1775.06</v>
+        <v>1794.91</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>4209.77</v>
+        <v>4256.85</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>1871.19</v>
+        <v>1892.12</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>5430.13</v>
+        <v>5490.86</v>
       </c>
     </row>
     <row r="266">
@@ -16673,13 +16673,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>15791.28</v>
+        <v>15967.89</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2292-6500-CM26</t>
+          <t>1075337-8153-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -16699,17 +16699,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K267" t="inlineStr"/>
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>8025.84</v>
+        <v>1052.1</v>
       </c>
     </row>
     <row r="268">
@@ -16795,13 +16795,13 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>809.12</v>
+        <v>815.25</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1075337-8153-CM26</t>
+          <t>2292-6500-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -16821,17 +16821,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -16841,12 +16841,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K269" t="inlineStr"/>
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>1044.19</v>
+        <v>8086.63</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>794</v>
+        <v>800.01</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>26280.64</v>
+        <v>26479.7</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1026.35</v>
+        <v>1030.24</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>851.45</v>
+        <v>854.67</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>26297.98</v>
+        <v>26231.59</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>9258.879999999999</v>
+        <v>9235.5</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>4098.01</v>
+        <v>4087.66</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>835.37</v>
+        <v>833.26</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>6254.75</v>
+        <v>6238.96</v>
       </c>
     </row>
     <row r="279">
@@ -17466,13 +17466,13 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>31073.47</v>
+        <v>30995.02</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1391-853-CM26</t>
+          <t>2294-480-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -17492,17 +17492,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>10034.87</v>
+        <v>34306.21</v>
       </c>
     </row>
     <row r="281">
@@ -17588,13 +17588,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>3824.38</v>
+        <v>3860.72</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2294-480-CM26</t>
+          <t>1391-853-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -17614,17 +17614,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>33983.34</v>
+        <v>10130.21</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>3319.49</v>
+        <v>3351.03</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>6449.54</v>
+        <v>6510.81</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>16804.86</v>
+        <v>16964.52</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>886.89</v>
+        <v>895.3200000000001</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>1243.03</v>
+        <v>1254.84</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>1136.92</v>
+        <v>1145.39</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1322.25</v>
+        <v>1332.11</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>1711.82</v>
+        <v>1724.57</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>954.39</v>
+        <v>961.5</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>7689.07</v>
+        <v>7612.39</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>3892.07</v>
+        <v>3853.26</v>
       </c>
     </row>
     <row r="294">
@@ -18381,13 +18381,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1211.26</v>
+        <v>1199.18</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2294-531-CM26</t>
+          <t>2294-472-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -18427,12 +18427,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>ANTALIS CHILE LIMITADA</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.305.910-1</t>
         </is>
       </c>
       <c r="K295" t="inlineStr"/>
@@ -18442,13 +18442,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>4375.21</v>
+        <v>1248.81</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2294-427-CM26</t>
+          <t>2294-531-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18488,12 +18488,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K296" t="inlineStr"/>
@@ -18503,13 +18503,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1949.84</v>
+        <v>4356.03</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2294-472-CM26</t>
+          <t>2294-427-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -18549,12 +18549,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>ANTALIS CHILE LIMITADA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>77.305.910-1</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K297" t="inlineStr"/>
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1254.31</v>
+        <v>1941.29</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>6824.47</v>
+        <v>6750.24</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1863.14</v>
+        <v>1858.54</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>7590.17</v>
+        <v>7571.43</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1113.45</v>
+        <v>1110.7</v>
       </c>
     </row>
     <row r="302">
@@ -18869,13 +18869,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>2137.02</v>
+        <v>2131.74</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>746-28-CM26</t>
+          <t>2440-661-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -18895,17 +18895,17 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18915,12 +18915,12 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K303" t="inlineStr"/>
@@ -18930,13 +18930,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1553.9</v>
+        <v>879.1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2440-661-CM26</t>
+          <t>746-28-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -18956,17 +18956,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18976,12 +18976,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K304" t="inlineStr"/>
@@ -18991,13 +18991,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>874.8</v>
+        <v>1561.54</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1607-57-CM26</t>
+          <t>2825-185-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -19017,17 +19017,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.509.000-k</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Superintendencia de Seguridad Social</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19037,12 +19037,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>93.558.000-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K305" t="inlineStr"/>
@@ -19052,13 +19052,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>2906.6</v>
+        <v>1131.18</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1596-141-CM26</t>
+          <t>2825-186-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -19078,17 +19078,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19098,12 +19098,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K306" t="inlineStr"/>
@@ -19113,13 +19113,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>2700.4</v>
+        <v>1155.79</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2825-186-CM26</t>
+          <t>1596-141-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -19139,17 +19139,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19159,12 +19159,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K307" t="inlineStr"/>
@@ -19174,13 +19174,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>1151.97</v>
+        <v>2709.36</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2825-185-CM26</t>
+          <t>1607-57-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -19200,17 +19200,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.509.000-k</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>Superintendencia de Seguridad Social</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19220,12 +19220,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DISTRIBUIDORA PAPELES INDUSTRIALES SPA</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>93.558.000-5</t>
         </is>
       </c>
       <c r="K308" t="inlineStr"/>
@@ -19235,13 +19235,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1127.44</v>
+        <v>2916.24</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1075337-8248-CM26</t>
+          <t>2292-6559-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -19261,17 +19261,17 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K309" t="inlineStr"/>
@@ -19296,13 +19296,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>3904.09</v>
+        <v>2325.27</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2440-701-CM26</t>
+          <t>2291-894-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -19322,17 +19322,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19342,12 +19342,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.437.580-3</t>
         </is>
       </c>
       <c r="K310" t="inlineStr"/>
@@ -19357,13 +19357,13 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>1088.8</v>
+        <v>2038.3</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2291-894-CM26</t>
+          <t>1075337-8248-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -19388,12 +19388,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K311" t="inlineStr"/>
@@ -19418,13 +19418,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2031.83</v>
+        <v>3916.51</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2292-6559-CM26</t>
+          <t>2440-701-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -19449,12 +19449,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>2317.9</v>
+        <v>1092.26</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>4615.93</v>
+        <v>4640.47</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>4693.29</v>
+        <v>4718.24</v>
       </c>
     </row>
     <row r="315">
@@ -19662,13 +19662,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>10328.94</v>
+        <v>10476.74</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2294-800-CM26</t>
+          <t>4452-372-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -19688,17 +19688,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K316" t="inlineStr"/>
@@ -19723,13 +19723,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>2313.26</v>
+        <v>1319.72</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>3876-112-CM26</t>
+          <t>3695-212-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -19754,12 +19754,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K317" t="inlineStr"/>
@@ -19784,13 +19784,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1932.17</v>
+        <v>2788.48</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>4452-372-CM26</t>
+          <t>2294-800-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -19810,17 +19810,17 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -19830,12 +19830,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K318" t="inlineStr"/>
@@ -19845,13 +19845,13 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>1297.77</v>
+        <v>2352.39</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>3695-212-CM26</t>
+          <t>3876-112-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -19876,12 +19876,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -19891,12 +19891,12 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K319" t="inlineStr"/>
@@ -19906,13 +19906,13 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>2742.11</v>
+        <v>1964.85</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2294-823-CM26</t>
+          <t>2827-412-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -19932,17 +19932,17 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -19952,12 +19952,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>76.452.485-3</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -19967,13 +19967,13 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>8634.459999999999</v>
+        <v>6721.99</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2294-826-CM26</t>
+          <t>4622-17-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -19993,17 +19993,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -20013,12 +20013,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -20028,13 +20028,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>1195.09</v>
+        <v>2055.28</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4622-17-CM26</t>
+          <t>2294-823-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20054,17 +20054,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -20074,12 +20074,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL IBL SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.452.485-3</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -20089,13 +20089,13 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2034.59</v>
+        <v>8722.27</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>2827-412-CM26</t>
+          <t>2294-826-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20115,17 +20115,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20135,12 +20135,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>6654.32</v>
+        <v>1207.24</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>897.78</v>
+        <v>906.21</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>894.8200000000001</v>
+        <v>903.21</v>
       </c>
     </row>
     <row r="326">
@@ -20333,13 +20333,13 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>940.83</v>
+        <v>949.66</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2291-1015-CM26</t>
+          <t>4316-20-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -20359,17 +20359,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20379,12 +20379,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.547.396-7</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K327" t="inlineStr"/>
@@ -20394,13 +20394,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1899.38</v>
+        <v>2095.26</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>4316-20-CM26</t>
+          <t>1233619-715-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20420,17 +20420,17 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>61.980.930-0</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -20455,13 +20455,13 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>2111.28</v>
+        <v>2722.06</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1233619-715-CM26</t>
+          <t>675-36-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -20486,12 +20486,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>61.980.930-0</t>
+          <t>61.402.019-9</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA MAULE COSTA</t>
+          <t>SEREMI Bienes Nacionales VII Región</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20501,12 +20501,12 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>77.610.393-4</t>
         </is>
       </c>
       <c r="K329" t="inlineStr"/>
@@ -20516,13 +20516,13 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>2742.87</v>
+        <v>880.45</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>675-36-CM26</t>
+          <t>2825-229-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -20542,17 +20542,17 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>61.402.019-9</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>SEREMI Bienes Nacionales VII Región</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -20562,12 +20562,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SAN JERONIMO SPA</t>
+          <t>LIBRERÍA GIORGIO LAGOS LIMITADA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>77.610.393-4</t>
+          <t>77.547.396-7</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -20577,13 +20577,13 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>887.1799999999999</v>
+        <v>1860.25</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>2825-229-CM26</t>
+          <t>2291-1015-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -20603,17 +20603,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -20638,13 +20638,13 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>1874.47</v>
+        <v>1884.97</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1391-1059-CM26</t>
+          <t>1596-149-CM26</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -20669,12 +20669,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Talca</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -20684,12 +20684,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.195.957-3</t>
         </is>
       </c>
       <c r="K332" t="inlineStr"/>
@@ -20699,13 +20699,13 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>5936.56</v>
+        <v>785.09</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1596-149-CM26</t>
+          <t>1391-1059-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -20730,12 +20730,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>Dirección Regional de Gendarmeria - Talca</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20745,12 +20745,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K333" t="inlineStr"/>
@@ -20760,13 +20760,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>798.58</v>
+        <v>5836.26</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>740-44-CM26</t>
+          <t>2294-1009-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -20786,17 +20786,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -20806,12 +20806,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K334" t="inlineStr"/>
@@ -20821,13 +20821,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>5176.22</v>
+        <v>9415.049999999999</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2294-1009-CM26</t>
+          <t>740-44-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -20847,17 +20847,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20867,12 +20867,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K335" t="inlineStr"/>
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>9473.780000000001</v>
+        <v>5144.13</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>793.61</v>
+        <v>797.22</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>1697.5</v>
+        <v>1722.77</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>795.34</v>
+        <v>813.27</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>985.3</v>
+        <v>1007.53</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1343.85</v>
+        <v>1374.15</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>6854.7</v>
+        <v>7009.29</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>2228.34</v>
+        <v>2278.6</v>
       </c>
     </row>
     <row r="343">
@@ -21370,13 +21370,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>3067</v>
+        <v>3136.17</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>4690-195-CM26</t>
+          <t>848-118-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -21396,17 +21396,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -21416,12 +21416,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>76.195.957-3</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K344" t="inlineStr"/>
@@ -21431,13 +21431,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4435.24</v>
+        <v>4486.42</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>848-120-CM26</t>
+          <t>4690-195-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -21457,17 +21457,17 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -21477,12 +21477,12 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>IMPORTADORA Y EXPORTADORA DURBAN LTDA</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>76.195.957-3</t>
         </is>
       </c>
       <c r="K345" t="inlineStr"/>
@@ -21492,13 +21492,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>4938.78</v>
+        <v>4465.87</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>848-119-CM26</t>
+          <t>848-120-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -21553,13 +21553,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>18241.15</v>
+        <v>4972.88</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3695-270-CM26</t>
+          <t>848-119-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -21584,12 +21584,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K347" t="inlineStr"/>
@@ -21614,13 +21614,13 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2631.9</v>
+        <v>18367.09</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>848-117-CM26</t>
+          <t>3695-270-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -21660,12 +21660,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K348" t="inlineStr"/>
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>10976.14</v>
+        <v>2650.07</v>
       </c>
     </row>
     <row r="349">
@@ -21736,13 +21736,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>796.2</v>
+        <v>801.7</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>848-118-CM26</t>
+          <t>848-117-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -21797,13 +21797,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>4455.66</v>
+        <v>11051.92</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>740-56-CM26</t>
+          <t>902-186-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -21823,17 +21823,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.307.000-1</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -21843,12 +21843,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K351" t="inlineStr"/>
@@ -21858,13 +21858,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>919.24</v>
+        <v>899.61</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2046-292-CM26</t>
+          <t>740-56-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -21889,12 +21889,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.307.000-1</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>INSTITUTO DE DESARROLLO AGROPECUARIO</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -21919,13 +21919,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>1560.34</v>
+        <v>922.08</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>848-121-CM26</t>
+          <t>2046-292-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -21950,12 +21950,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -21965,12 +21965,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.461.733-7</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K353" t="inlineStr"/>
@@ -21980,13 +21980,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>24427.43</v>
+        <v>1565.17</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>848-122-CM26</t>
+          <t>848-121-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22041,13 +22041,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>4862.07</v>
+        <v>24502.95</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>902-186-CM26</t>
+          <t>848-122-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22067,17 +22067,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22087,12 +22087,12 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>IMPORTADORA Y COMERCIALIZADORA JMMB SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.461.733-7</t>
         </is>
       </c>
       <c r="K355" t="inlineStr"/>
@@ -22102,13 +22102,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>896.83</v>
+        <v>4877.1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2294-1113-CM26</t>
+          <t>1069417-686-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22128,17 +22128,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.270.200-k</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>Dirección  de Salud Municipal Chillán</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22148,12 +22148,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>4775.24</v>
+        <v>2227.55</v>
       </c>
     </row>
     <row r="357">
@@ -22224,13 +22224,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>1519.54</v>
+        <v>1515.52</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1069417-686-CM26</t>
+          <t>1069417-685-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22270,12 +22270,12 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K358" t="inlineStr"/>
@@ -22285,13 +22285,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>2233.46</v>
+        <v>1199.68</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1069417-685-CM26</t>
+          <t>2294-1113-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22311,17 +22311,17 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>69.270.200-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Dirección  de Salud Municipal Chillán</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22331,12 +22331,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22346,13 +22346,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1202.86</v>
+        <v>4762.61</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>2294-1131-CM26</t>
+          <t>2294-1132-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22392,12 +22392,12 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>BAILEY GROUP SPA</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>77.638.992-7</t>
         </is>
       </c>
       <c r="K360" t="inlineStr"/>
@@ -22407,13 +22407,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1736.56</v>
+        <v>987.5599999999999</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>2294-1132-CM26</t>
+          <t>2294-1131-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -22453,12 +22453,12 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>BAILEY GROUP SPA</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.638.992-7</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K361" t="inlineStr"/>
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1000.89</v>
+        <v>1713.42</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3768.05</v>
+        <v>3694.29</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2463.95</v>
+        <v>2415.72</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>2585.52</v>
+        <v>2534.91</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1338.55</v>
+        <v>1318.72</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>3637.89</v>
+        <v>3583.99</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>3319.43</v>
+        <v>3270.25</v>
       </c>
     </row>
     <row r="368">
@@ -22895,13 +22895,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3617.54</v>
+        <v>3563.94</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>4451-367-CM26</t>
+          <t>2294-1138-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -22921,17 +22921,17 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -22941,12 +22941,12 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>COMERCIAL VALLE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>77.988.165-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K369" t="inlineStr"/>
@@ -22956,13 +22956,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>16553.29</v>
+        <v>960.87</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2294-1138-CM26</t>
+          <t>4451-367-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -22982,17 +22982,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23002,12 +23002,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL VALLE SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.988.165-2</t>
         </is>
       </c>
       <c r="K370" t="inlineStr"/>
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>981.04</v>
+        <v>16213.1</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>3380.51</v>
+        <v>3412.62</v>
       </c>
     </row>
     <row r="372">
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>814.15</v>
+        <v>821.88</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3806-94-CM26</t>
+          <t>902-206-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -23170,12 +23170,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -23185,12 +23185,12 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K373" t="inlineStr"/>
@@ -23200,13 +23200,13 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>856.65</v>
+        <v>902.5</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3287-328-CM26</t>
+          <t>3806-94-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23226,17 +23226,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23246,12 +23246,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K374" t="inlineStr"/>
@@ -23261,13 +23261,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>1548</v>
+        <v>860</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>902-206-CM26</t>
+          <t>3287-328-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23287,17 +23287,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23307,12 +23307,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.437.580-3</t>
         </is>
       </c>
       <c r="K375" t="inlineStr"/>
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>898.99</v>
+        <v>1554.04</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>7170.91</v>
+        <v>7243.03</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2893.81</v>
+        <v>2922.91</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>8378.42</v>
+        <v>8462.690000000001</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1209.8</v>
+        <v>1221.97</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>783.55</v>
+        <v>791.39</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2440.47</v>
+        <v>2449.97</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>9412.26</v>
+        <v>9364.58</v>
       </c>
     </row>
     <row r="383">
@@ -23810,13 +23810,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>1355.23</v>
+        <v>1364.06</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4452-601-CM26</t>
+          <t>3206-257-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -23841,12 +23841,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>69.264.500-6</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -23856,12 +23856,12 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
+          <t>LIBRERÍA ATLANTIK LIMITADA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>76.540.457-6</t>
+          <t>76.943.080-6</t>
         </is>
       </c>
       <c r="K384" t="inlineStr"/>
@@ -23871,13 +23871,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>16228.49</v>
+        <v>2619.6</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>2294-1277-CM26</t>
+          <t>1681-501-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -23897,17 +23897,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -23932,13 +23932,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>2992.99</v>
+        <v>7569.78</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1681-501-CM26</t>
+          <t>4452-601-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -23993,13 +23993,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>7552.46</v>
+        <v>16265.71</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3206-257-CM26</t>
+          <t>2294-1277-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24019,17 +24019,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>69.264.500-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN RAFAEL</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24039,12 +24039,12 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>LIBRERÍA ATLANTIK LIMITADA</t>
+          <t>SOCIEDAD SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>76.943.080-6</t>
+          <t>76.540.457-6</t>
         </is>
       </c>
       <c r="K387" t="inlineStr"/>
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>2613.61</v>
+        <v>2999.85</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1327.01</v>
+        <v>1335.9</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1616.79</v>
+        <v>1627.61</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1108.23</v>
+        <v>1115.65</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>792.86</v>
+        <v>798.17</v>
       </c>
     </row>
     <row r="392">
@@ -24359,13 +24359,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>1244.81</v>
+        <v>1240.88</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>439-372-CM26</t>
+          <t>4451-415-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -24390,12 +24390,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>69.110.200-9</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24405,12 +24405,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>Papeles Cono Sur Ltda.</t>
+          <t>AMINORTE S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>78.437.580-3</t>
+          <t>99.533.780-0</t>
         </is>
       </c>
       <c r="K393" t="inlineStr"/>
@@ -24420,13 +24420,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>4290.75</v>
+        <v>2035.31</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>902-223-CM26</t>
+          <t>1978-750-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -24451,12 +24451,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -24466,12 +24466,12 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K394" t="inlineStr"/>
@@ -24481,13 +24481,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>796.74</v>
+        <v>19058.57</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>4451-415-CM26</t>
+          <t>1681-524-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -24512,12 +24512,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24527,12 +24527,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>AMINORTE S A</t>
+          <t>OTTO HAN SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>99.533.780-0</t>
+          <t>77.809.872-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr"/>
@@ -24542,13 +24542,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2039.4</v>
+        <v>1374.38</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1681-524-CM26</t>
+          <t>902-223-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -24573,12 +24573,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -24588,12 +24588,12 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>OTTO HAN SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>77.809.872-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K396" t="inlineStr"/>
@@ -24603,13 +24603,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>1377.14</v>
+        <v>795.15</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1978-750-CM26</t>
+          <t>439-372-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -24634,12 +24634,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.110.200-9</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I. Municipalidad Sagrada Familia</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -24649,12 +24649,12 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Papeles Cono Sur Ltda.</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.437.580-3</t>
         </is>
       </c>
       <c r="K397" t="inlineStr"/>
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>19096.86</v>
+        <v>4282.15</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>852.85</v>
+        <v>847.91</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>2564.78</v>
+        <v>2549.94</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>771.58</v>
+        <v>759.13</v>
       </c>
     </row>
     <row r="401">
@@ -24908,13 +24908,13 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1118.74</v>
+        <v>1100.69</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>834259-46-CM26</t>
+          <t>2595-303-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -24939,12 +24939,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>69.100.300-0</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TENO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -24954,12 +24954,12 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K402" t="inlineStr"/>
@@ -24969,13 +24969,13 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>3048.13</v>
+        <v>1674.41</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2440-1109-CM26</t>
+          <t>2595-302-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25000,12 +25000,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25015,12 +25015,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K403" t="inlineStr"/>
@@ -25030,13 +25030,13 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2047.74</v>
+        <v>2079.25</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2595-302-CM26</t>
+          <t>2595-304-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.547.399-1</t>
         </is>
       </c>
       <c r="K404" t="inlineStr"/>
@@ -25091,13 +25091,13 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>2090.84</v>
+        <v>1042.45</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>2595-303-CM26</t>
+          <t>834259-46-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -25122,12 +25122,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.300-0</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE TENO</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -25137,12 +25137,12 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K405" t="inlineStr"/>
@@ -25152,13 +25152,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>1683.74</v>
+        <v>3031.24</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>2595-304-CM26</t>
+          <t>2440-1109-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -25183,12 +25183,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25198,12 +25198,12 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>LIBRERÍA GIORGIO CHILLÁN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>77.547.399-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K406" t="inlineStr"/>
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>1048.26</v>
+        <v>2036.38</v>
       </c>
     </row>
     <row r="407">
@@ -25274,13 +25274,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1197.01</v>
+        <v>1191.13</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>4476-136-CM26</t>
+          <t>4476-139-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25320,12 +25320,12 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA VERGIO SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>96.972.190-2</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K408" t="inlineStr"/>
@@ -25335,13 +25335,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1024.95</v>
+        <v>3180.38</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>4476-139-CM26</t>
+          <t>4476-136-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -25381,12 +25381,12 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DISTRIBUIDORA VERGIO SPA</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.972.190-2</t>
         </is>
       </c>
       <c r="K409" t="inlineStr"/>
@@ -25396,7 +25396,68 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3159.23</v>
+        <v>1031.81</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>1069417-918-CM26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2239-16-LR24</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>69.270.200-k</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILLAN</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M410" s="2" t="n">
+        <v>1118.48</v>
       </c>
     </row>
   </sheetData>
